--- a/material/febrero-4/premise/Ejercicio practico/parametric_lca_v0.xlsx
+++ b/material/febrero-4/premise/Ejercicio practico/parametric_lca_v0.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FB8C27-5AAD-4D83-B52A-9764F8EB4256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{958B7F32-0D22-4C8B-BD0A-0290E18CB9E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3705" yWindow="-21720" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Process data" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="52">
   <si>
     <t>Activity</t>
   </si>
@@ -186,16 +186,7 @@
     <t>Particulate Matter, &lt; 2.5 um</t>
   </si>
   <si>
-    <t>comment formula</t>
-  </si>
-  <si>
     <t>parametric_LCA</t>
-  </si>
-  <si>
-    <t>Parameters</t>
-  </si>
-  <si>
-    <t>ev_group</t>
   </si>
 </sst>
 </file>
@@ -249,7 +240,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -274,12 +265,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -294,7 +279,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -316,12 +301,6 @@
     </xf>
     <xf numFmtId="11" fontId="2" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -603,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P313"/>
+  <dimension ref="A1:P309"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="63.42578125" style="2" customWidth="1"/>
@@ -623,7 +602,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
@@ -1407,73 +1386,100 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21"/>
-      <c r="H37" s="21"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="14"/>
-      <c r="N37" s="14"/>
-      <c r="O37" s="14"/>
+        <v>11</v>
+      </c>
+      <c r="B37" s="15"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
+      <c r="M37" s="15"/>
+      <c r="N37" s="15"/>
+      <c r="O37" s="15"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="19" t="s">
+      <c r="A38" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="C38" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D38" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D38" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="E38" s="19" t="s">
+      <c r="E38" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H38" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="I38" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="J38" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="19" t="s">
+      <c r="K38" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="G38" s="19" t="s">
+      <c r="L38" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="H38" s="19" t="s">
+      <c r="M38" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="I38" s="19" t="s">
+      <c r="N38" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="J38" s="19" t="s">
+      <c r="O38" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
-      <c r="N38" s="15"/>
-      <c r="O38" s="15"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="22"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="22"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="22"/>
-      <c r="J39" s="22"/>
+      <c r="A39" s="15" t="str">
+        <f>B29</f>
+        <v>driving the EV</v>
+      </c>
+      <c r="B39" s="15">
+        <f>160000/160000</f>
+        <v>1</v>
+      </c>
+      <c r="C39" s="15" t="str">
+        <f>B30</f>
+        <v>CH</v>
+      </c>
+      <c r="D39" s="15" t="str">
+        <f>B35</f>
+        <v>kilometer</v>
+      </c>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="15" t="str">
+        <f>B33</f>
+        <v>kilometers</v>
+      </c>
+      <c r="H39" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
       <c r="K39" s="15"/>
       <c r="L39" s="15"/>
       <c r="M39" s="15"/>
@@ -1481,14 +1487,29 @@
       <c r="O39" s="15"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="15"/>
-      <c r="B40" s="16"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
+      <c r="A40" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B40" s="15">
+        <f>1/160000</f>
+        <v>6.2500000000000003E-6</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>9</v>
+      </c>
       <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
+      <c r="F40" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H40" s="15" t="s">
+        <v>23</v>
+      </c>
       <c r="I40" s="15"/>
       <c r="J40" s="15"/>
       <c r="K40" s="15"/>
@@ -1498,16 +1519,29 @@
       <c r="O40" s="15"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
+      <c r="A41" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="15">
+        <f>31500/160000</f>
+        <v>0.19687499999999999</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>22</v>
+      </c>
       <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="15"/>
+      <c r="F41" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H41" s="15" t="s">
+        <v>49</v>
+      </c>
       <c r="I41" s="15"/>
       <c r="J41" s="15"/>
       <c r="K41" s="15"/>
@@ -1517,161 +1551,96 @@
       <c r="O41" s="15"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="14" t="s">
+      <c r="B42" s="8"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12"/>
+      <c r="L43" s="12"/>
+      <c r="M43" s="12"/>
+      <c r="N43" s="12"/>
+      <c r="O43" s="12"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D42" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F42" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="G42" s="14" t="s">
+      <c r="B44" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="12"/>
+      <c r="K44" s="12"/>
+      <c r="L44" s="12"/>
+      <c r="M44" s="12"/>
+      <c r="N44" s="12"/>
+      <c r="O44" s="12"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B45" s="12">
+        <v>1</v>
+      </c>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="12"/>
+      <c r="K45" s="12"/>
+      <c r="L45" s="12"/>
+      <c r="M45" s="12"/>
+      <c r="N45" s="12"/>
+      <c r="O45" s="12"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12"/>
+      <c r="L46" s="12"/>
+      <c r="M46" s="12"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="12"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H42" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="I42" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="J42" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="K42" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="L42" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="M42" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="N42" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="O42" s="15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="15" t="str">
-        <f>B29</f>
-        <v>driving the EV</v>
-      </c>
-      <c r="B43" s="15">
-        <f>160000/160000</f>
-        <v>1</v>
-      </c>
-      <c r="C43" s="15" t="str">
-        <f>B30</f>
-        <v>CH</v>
-      </c>
-      <c r="D43" s="15" t="str">
-        <f>B35</f>
-        <v>kilometer</v>
-      </c>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G43" s="15" t="str">
-        <f>B33</f>
-        <v>kilometers</v>
-      </c>
-      <c r="H43" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
-      <c r="K43" s="15"/>
-      <c r="L43" s="15"/>
-      <c r="M43" s="15"/>
-      <c r="N43" s="15"/>
-      <c r="O43" s="15"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B44" s="15">
-        <f>1/160000</f>
-        <v>6.2500000000000003E-6</v>
-      </c>
-      <c r="C44" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G44" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="H44" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="I44" s="15"/>
-      <c r="J44" s="15"/>
-      <c r="K44" s="15"/>
-      <c r="L44" s="15"/>
-      <c r="M44" s="15"/>
-      <c r="N44" s="15"/>
-      <c r="O44" s="15"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="B45" s="15">
-        <f>31500/160000</f>
-        <v>0.19687499999999999</v>
-      </c>
-      <c r="C45" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D45" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G45" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="H45" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15"/>
-      <c r="K45" s="15"/>
-      <c r="L45" s="15"/>
-      <c r="M45" s="15"/>
-      <c r="N45" s="15"/>
-      <c r="O45" s="15"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B46" s="8"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A47" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B47" s="11" t="s">
-        <v>35</v>
+      <c r="B47" s="12" t="s">
+        <v>36</v>
       </c>
       <c r="C47" s="12"/>
       <c r="D47" s="12"/>
@@ -1689,10 +1658,10 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
@@ -1710,10 +1679,10 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B49" s="12">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
@@ -1730,8 +1699,8 @@
       <c r="O49" s="12"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="12" t="s">
-        <v>5</v>
+      <c r="A50" s="11" t="s">
+        <v>11</v>
       </c>
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
@@ -1749,39 +1718,79 @@
       <c r="O50" s="12"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="12" t="s">
+      <c r="A51" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G51" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B51" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12"/>
-      <c r="I51" s="12"/>
-      <c r="J51" s="12"/>
-      <c r="K51" s="12"/>
-      <c r="L51" s="12"/>
-      <c r="M51" s="12"/>
-      <c r="N51" s="12"/>
-      <c r="O51" s="12"/>
+      <c r="H51" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M51" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="N51" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="O51" s="11" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
+      <c r="A52" s="12" t="str">
+        <f>B43</f>
+        <v>ICEV production</v>
+      </c>
+      <c r="B52" s="12">
+        <v>1</v>
+      </c>
+      <c r="C52" s="12" t="str">
+        <f>B44</f>
+        <v>CH</v>
+      </c>
+      <c r="D52" s="12" t="str">
+        <f>B49</f>
+        <v>unit</v>
+      </c>
       <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
+      <c r="F52" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G52" s="12" t="str">
+        <f>B47</f>
+        <v>diesel vehicle</v>
+      </c>
+      <c r="H52" s="12" t="s">
+        <v>23</v>
+      </c>
       <c r="I52" s="12"/>
       <c r="J52" s="12"/>
       <c r="K52" s="12"/>
@@ -1792,17 +1801,27 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
+        <v>48</v>
+      </c>
+      <c r="B53" s="12">
+        <v>3000</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>22</v>
+      </c>
       <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="12"/>
+      <c r="F53" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G53" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H53" s="12" t="s">
+        <v>29</v>
+      </c>
       <c r="I53" s="12"/>
       <c r="J53" s="12"/>
       <c r="K53" s="12"/>
@@ -1811,144 +1830,94 @@
       <c r="N53" s="12"/>
       <c r="O53" s="12"/>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B54" s="12"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
-      <c r="K54" s="12"/>
-      <c r="L54" s="12"/>
-      <c r="M54" s="12"/>
-      <c r="N54" s="12"/>
-      <c r="O54" s="12"/>
-    </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B55" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" s="11" t="s">
+      <c r="A55" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B55" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="15"/>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
+      <c r="J55" s="15"/>
+      <c r="K55" s="15"/>
+      <c r="L55" s="15"/>
+      <c r="M55" s="15"/>
+      <c r="N55" s="15"/>
+      <c r="O55" s="15"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D55" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E55" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F55" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G55" s="11" t="s">
+      <c r="B56" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" s="15"/>
+      <c r="D56" s="15"/>
+      <c r="E56" s="15"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="15"/>
+      <c r="H56" s="15"/>
+      <c r="I56" s="15"/>
+      <c r="J56" s="15"/>
+      <c r="K56" s="15"/>
+      <c r="L56" s="15"/>
+      <c r="M56" s="15"/>
+      <c r="N56" s="15"/>
+      <c r="O56" s="15"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B57" s="15">
+        <v>1</v>
+      </c>
+      <c r="C57" s="15"/>
+      <c r="D57" s="15"/>
+      <c r="E57" s="15"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="15"/>
+      <c r="H57" s="15"/>
+      <c r="I57" s="15"/>
+      <c r="J57" s="15"/>
+      <c r="K57" s="15"/>
+      <c r="L57" s="15"/>
+      <c r="M57" s="15"/>
+      <c r="N57" s="15"/>
+      <c r="O57" s="15"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B58" s="15"/>
+      <c r="C58" s="15"/>
+      <c r="D58" s="15"/>
+      <c r="E58" s="15"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="15"/>
+      <c r="H58" s="15"/>
+      <c r="I58" s="15"/>
+      <c r="J58" s="15"/>
+      <c r="K58" s="15"/>
+      <c r="L58" s="15"/>
+      <c r="M58" s="15"/>
+      <c r="N58" s="15"/>
+      <c r="O58" s="15"/>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H55" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="I55" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J55" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="K55" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="L55" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="M55" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="N55" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="O55" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="12" t="str">
-        <f>B47</f>
-        <v>ICEV production</v>
-      </c>
-      <c r="B56" s="12">
-        <v>1</v>
-      </c>
-      <c r="C56" s="12" t="str">
-        <f>B48</f>
-        <v>CH</v>
-      </c>
-      <c r="D56" s="12" t="str">
-        <f>B53</f>
-        <v>unit</v>
-      </c>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G56" s="12" t="str">
-        <f>B51</f>
-        <v>diesel vehicle</v>
-      </c>
-      <c r="H56" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
-      <c r="K56" s="12"/>
-      <c r="L56" s="12"/>
-      <c r="M56" s="12"/>
-      <c r="N56" s="12"/>
-      <c r="O56" s="12"/>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B57" s="12">
-        <v>3000</v>
-      </c>
-      <c r="C57" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G57" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="H57" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
-      <c r="K57" s="12"/>
-      <c r="L57" s="12"/>
-      <c r="M57" s="12"/>
-      <c r="N57" s="12"/>
-      <c r="O57" s="12"/>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B59" s="14" t="s">
-        <v>37</v>
+      <c r="B59" s="15" t="s">
+        <v>39</v>
       </c>
       <c r="C59" s="15"/>
       <c r="D59" s="15"/>
@@ -1966,10 +1935,10 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C60" s="15"/>
       <c r="D60" s="15"/>
@@ -1987,10 +1956,10 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B61" s="15">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="C61" s="15"/>
       <c r="D61" s="15"/>
@@ -2007,8 +1976,8 @@
       <c r="O61" s="15"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="15" t="s">
-        <v>5</v>
+      <c r="A62" s="14" t="s">
+        <v>11</v>
       </c>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
@@ -2026,39 +1995,79 @@
       <c r="O62" s="15"/>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="15" t="s">
+      <c r="A63" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B63" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D63" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F63" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="G63" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B63" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C63" s="15"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="15"/>
-      <c r="G63" s="15"/>
-      <c r="H63" s="15"/>
-      <c r="I63" s="15"/>
-      <c r="J63" s="15"/>
-      <c r="K63" s="15"/>
-      <c r="L63" s="15"/>
-      <c r="M63" s="15"/>
-      <c r="N63" s="15"/>
-      <c r="O63" s="15"/>
+      <c r="H63" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="I63" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="J63" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="K63" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="L63" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="M63" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="N63" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="O63" s="14" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B64" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C64" s="15"/>
-      <c r="D64" s="15"/>
+      <c r="A64" s="15" t="str">
+        <f>B55</f>
+        <v>diesel supply</v>
+      </c>
+      <c r="B64" s="15">
+        <v>1</v>
+      </c>
+      <c r="C64" s="15" t="str">
+        <f>B56</f>
+        <v>CH</v>
+      </c>
+      <c r="D64" s="15" t="str">
+        <f>B61</f>
+        <v>kilogram</v>
+      </c>
       <c r="E64" s="15"/>
-      <c r="F64" s="15"/>
-      <c r="G64" s="15"/>
-      <c r="H64" s="15"/>
+      <c r="F64" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G64" s="15" t="str">
+        <f>B59</f>
+        <v>diesel</v>
+      </c>
+      <c r="H64" s="15" t="s">
+        <v>23</v>
+      </c>
       <c r="I64" s="15"/>
       <c r="J64" s="15"/>
       <c r="K64" s="15"/>
@@ -2069,17 +2078,27 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B65" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C65" s="15"/>
-      <c r="D65" s="15"/>
+        <v>48</v>
+      </c>
+      <c r="B65" s="15">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D65" s="15" t="s">
+        <v>22</v>
+      </c>
       <c r="E65" s="15"/>
-      <c r="F65" s="15"/>
-      <c r="G65" s="15"/>
-      <c r="H65" s="15"/>
+      <c r="F65" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G65" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H65" s="15" t="s">
+        <v>29</v>
+      </c>
       <c r="I65" s="15"/>
       <c r="J65" s="15"/>
       <c r="K65" s="15"/>
@@ -2089,16 +2108,26 @@
       <c r="O65" s="15"/>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A66" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B66" s="15"/>
+      <c r="A66" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B66" s="17">
+        <v>2.0000000000000002E-5</v>
+      </c>
       <c r="C66" s="15"/>
-      <c r="D66" s="15"/>
-      <c r="E66" s="15"/>
-      <c r="F66" s="15"/>
+      <c r="D66" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E66" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F66" s="15" t="s">
+        <v>17</v>
+      </c>
       <c r="G66" s="15"/>
-      <c r="H66" s="15"/>
+      <c r="H66" s="15" t="s">
+        <v>24</v>
+      </c>
       <c r="I66" s="15"/>
       <c r="J66" s="15"/>
       <c r="K66" s="15"/>
@@ -2108,187 +2137,127 @@
       <c r="O66" s="15"/>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A67" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B67" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" s="14" t="s">
+      <c r="A67" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B67" s="17">
+        <v>1.5E-6</v>
+      </c>
+      <c r="C67" s="15"/>
+      <c r="D67" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E67" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F67" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G67" s="15"/>
+      <c r="H67" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I67" s="15"/>
+      <c r="J67" s="15"/>
+      <c r="K67" s="15"/>
+      <c r="L67" s="15"/>
+      <c r="M67" s="15"/>
+      <c r="N67" s="15"/>
+      <c r="O67" s="15"/>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68" s="7"/>
+      <c r="B68" s="3"/>
+      <c r="H68" s="3"/>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="12"/>
+      <c r="D69" s="12"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="12"/>
+      <c r="I69" s="12"/>
+      <c r="J69" s="12"/>
+      <c r="K69" s="12"/>
+      <c r="L69" s="12"/>
+      <c r="M69" s="12"/>
+      <c r="N69" s="12"/>
+      <c r="O69" s="12"/>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D67" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E67" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F67" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="G67" s="14" t="s">
+      <c r="B70" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C70" s="12"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
+      <c r="H70" s="12"/>
+      <c r="I70" s="12"/>
+      <c r="J70" s="12"/>
+      <c r="K70" s="12"/>
+      <c r="L70" s="12"/>
+      <c r="M70" s="12"/>
+      <c r="N70" s="12"/>
+      <c r="O70" s="12"/>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B71" s="12">
+        <v>1</v>
+      </c>
+      <c r="C71" s="12"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
+      <c r="H71" s="12"/>
+      <c r="I71" s="12"/>
+      <c r="J71" s="12"/>
+      <c r="K71" s="12"/>
+      <c r="L71" s="12"/>
+      <c r="M71" s="12"/>
+      <c r="N71" s="12"/>
+      <c r="O71" s="12"/>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A72" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B72" s="12"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12"/>
+      <c r="H72" s="12"/>
+      <c r="I72" s="12"/>
+      <c r="J72" s="12"/>
+      <c r="K72" s="12"/>
+      <c r="L72" s="12"/>
+      <c r="M72" s="12"/>
+      <c r="N72" s="12"/>
+      <c r="O72" s="12"/>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A73" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H67" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="I67" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J67" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="K67" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="L67" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="M67" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="N67" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="O67" s="14" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A68" s="15" t="str">
-        <f>B59</f>
-        <v>diesel supply</v>
-      </c>
-      <c r="B68" s="15">
-        <v>1</v>
-      </c>
-      <c r="C68" s="15" t="str">
-        <f>B60</f>
-        <v>CH</v>
-      </c>
-      <c r="D68" s="15" t="str">
-        <f>B65</f>
-        <v>kilogram</v>
-      </c>
-      <c r="E68" s="15"/>
-      <c r="F68" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G68" s="15" t="str">
-        <f>B63</f>
-        <v>diesel</v>
-      </c>
-      <c r="H68" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="I68" s="15"/>
-      <c r="J68" s="15"/>
-      <c r="K68" s="15"/>
-      <c r="L68" s="15"/>
-      <c r="M68" s="15"/>
-      <c r="N68" s="15"/>
-      <c r="O68" s="15"/>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="B69" s="15">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="C69" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D69" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E69" s="15"/>
-      <c r="F69" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G69" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="H69" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="I69" s="15"/>
-      <c r="J69" s="15"/>
-      <c r="K69" s="15"/>
-      <c r="L69" s="15"/>
-      <c r="M69" s="15"/>
-      <c r="N69" s="15"/>
-      <c r="O69" s="15"/>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B70" s="17">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="C70" s="15"/>
-      <c r="D70" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E70" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="F70" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="G70" s="15"/>
-      <c r="H70" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="I70" s="15"/>
-      <c r="J70" s="15"/>
-      <c r="K70" s="15"/>
-      <c r="L70" s="15"/>
-      <c r="M70" s="15"/>
-      <c r="N70" s="15"/>
-      <c r="O70" s="15"/>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B71" s="17">
-        <v>1.5E-6</v>
-      </c>
-      <c r="C71" s="15"/>
-      <c r="D71" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E71" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="F71" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="G71" s="15"/>
-      <c r="H71" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="I71" s="15"/>
-      <c r="J71" s="15"/>
-      <c r="K71" s="15"/>
-      <c r="L71" s="15"/>
-      <c r="M71" s="15"/>
-      <c r="N71" s="15"/>
-      <c r="O71" s="15"/>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A72" s="7"/>
-      <c r="B72" s="3"/>
-      <c r="H72" s="3"/>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A73" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B73" s="11" t="s">
-        <v>38</v>
+      <c r="B73" s="12" t="s">
+        <v>33</v>
       </c>
       <c r="C73" s="12"/>
       <c r="D73" s="12"/>
@@ -2306,10 +2275,10 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C74" s="12"/>
       <c r="D74" s="12"/>
@@ -2327,10 +2296,10 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B75" s="12">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>34</v>
       </c>
       <c r="C75" s="12"/>
       <c r="D75" s="12"/>
@@ -2347,8 +2316,8 @@
       <c r="O75" s="12"/>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A76" s="12" t="s">
-        <v>5</v>
+      <c r="A76" s="11" t="s">
+        <v>11</v>
       </c>
       <c r="B76" s="12"/>
       <c r="C76" s="12"/>
@@ -2366,39 +2335,80 @@
       <c r="O76" s="12"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" s="12" t="s">
+      <c r="A77" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F77" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G77" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B77" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C77" s="12"/>
-      <c r="D77" s="12"/>
-      <c r="E77" s="12"/>
-      <c r="F77" s="12"/>
-      <c r="G77" s="12"/>
-      <c r="H77" s="12"/>
-      <c r="I77" s="12"/>
-      <c r="J77" s="12"/>
-      <c r="K77" s="12"/>
-      <c r="L77" s="12"/>
-      <c r="M77" s="12"/>
-      <c r="N77" s="12"/>
-      <c r="O77" s="12"/>
+      <c r="H77" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="I77" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J77" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K77" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="L77" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M77" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="N77" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="O77" s="11" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A78" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B78" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C78" s="12"/>
-      <c r="D78" s="12"/>
+      <c r="A78" s="12" t="str">
+        <f>B69</f>
+        <v>driving the ICEV</v>
+      </c>
+      <c r="B78" s="12">
+        <f>160000/160000</f>
+        <v>1</v>
+      </c>
+      <c r="C78" s="12" t="str">
+        <f>B70</f>
+        <v>CH</v>
+      </c>
+      <c r="D78" s="12" t="str">
+        <f>B75</f>
+        <v>kilometer</v>
+      </c>
       <c r="E78" s="12"/>
-      <c r="F78" s="12"/>
-      <c r="G78" s="12"/>
-      <c r="H78" s="12"/>
+      <c r="F78" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G78" s="12" t="str">
+        <f>B73</f>
+        <v>kilometers</v>
+      </c>
+      <c r="H78" s="12" t="s">
+        <v>23</v>
+      </c>
       <c r="I78" s="12"/>
       <c r="J78" s="12"/>
       <c r="K78" s="12"/>
@@ -2409,17 +2419,28 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B79" s="12">
+        <f>1/160000</f>
+        <v>6.2500000000000003E-6</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D79" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B79" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C79" s="12"/>
-      <c r="D79" s="12"/>
       <c r="E79" s="12"/>
-      <c r="F79" s="12"/>
-      <c r="G79" s="12"/>
-      <c r="H79" s="12"/>
+      <c r="F79" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G79" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H79" s="12" t="s">
+        <v>29</v>
+      </c>
       <c r="I79" s="12"/>
       <c r="J79" s="12"/>
       <c r="K79" s="12"/>
@@ -2429,16 +2450,29 @@
       <c r="O79" s="12"/>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A80" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B80" s="12"/>
-      <c r="C80" s="12"/>
-      <c r="D80" s="12"/>
+      <c r="A80" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B80" s="12">
+        <f>12200/160000</f>
+        <v>7.6249999999999998E-2</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>10</v>
+      </c>
       <c r="E80" s="12"/>
-      <c r="F80" s="12"/>
-      <c r="G80" s="12"/>
-      <c r="H80" s="12"/>
+      <c r="F80" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G80" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H80" s="12" t="s">
+        <v>29</v>
+      </c>
       <c r="I80" s="12"/>
       <c r="J80" s="12"/>
       <c r="K80" s="12"/>
@@ -2448,79 +2482,56 @@
       <c r="O80" s="12"/>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A81" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B81" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C81" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D81" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E81" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F81" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G81" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="H81" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="I81" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J81" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="K81" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="L81" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="M81" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="N81" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="O81" s="11" t="s">
-        <v>46</v>
-      </c>
+      <c r="A81" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B81" s="13">
+        <f>38000/160000</f>
+        <v>0.23749999999999999</v>
+      </c>
+      <c r="C81" s="12"/>
+      <c r="D81" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E81" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F81" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G81" s="12"/>
+      <c r="H81" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I81" s="12"/>
+      <c r="J81" s="12"/>
+      <c r="K81" s="12"/>
+      <c r="L81" s="12"/>
+      <c r="M81" s="12"/>
+      <c r="N81" s="12"/>
+      <c r="O81" s="12"/>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A82" s="12" t="str">
-        <f>B73</f>
-        <v>driving the ICEV</v>
-      </c>
-      <c r="B82" s="12">
-        <f>160000/160000</f>
-        <v>1</v>
-      </c>
-      <c r="C82" s="12" t="str">
-        <f>B74</f>
-        <v>CH</v>
-      </c>
-      <c r="D82" s="12" t="str">
-        <f>B79</f>
-        <v>kilometer</v>
-      </c>
-      <c r="E82" s="12"/>
+      <c r="A82" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B82" s="13">
+        <f>0.008/160000</f>
+        <v>4.9999999999999998E-8</v>
+      </c>
+      <c r="C82" s="12"/>
+      <c r="D82" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E82" s="12" t="s">
+        <v>18</v>
+      </c>
       <c r="F82" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G82" s="12" t="str">
-        <f>B77</f>
-        <v>kilometers</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="G82" s="12"/>
       <c r="H82" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I82" s="12"/>
       <c r="J82" s="12"/>
@@ -2532,27 +2543,25 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B83" s="12">
-        <f>1/160000</f>
-        <v>6.2500000000000003E-6</v>
-      </c>
-      <c r="C83" s="12" t="s">
-        <v>20</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B83" s="13">
+        <f>B80*0.0015</f>
+        <v>1.14375E-4</v>
+      </c>
+      <c r="C83" s="12"/>
       <c r="D83" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E83" s="12"/>
+        <v>10</v>
+      </c>
+      <c r="E83" s="12" t="s">
+        <v>18</v>
+      </c>
       <c r="F83" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G83" s="12" t="s">
-        <v>36</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="G83" s="12"/>
       <c r="H83" s="12" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I83" s="12"/>
       <c r="J83" s="12"/>
@@ -2562,314 +2571,202 @@
       <c r="N83" s="12"/>
       <c r="O83" s="12"/>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A84" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B84" s="12">
-        <f>12200/160000</f>
-        <v>7.6249999999999998E-2</v>
-      </c>
-      <c r="C84" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D84" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E84" s="12"/>
-      <c r="F84" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G84" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H84" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="I84" s="12"/>
-      <c r="J84" s="12"/>
-      <c r="K84" s="12"/>
-      <c r="L84" s="12"/>
-      <c r="M84" s="12"/>
-      <c r="N84" s="12"/>
-      <c r="O84" s="12"/>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A85" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B85" s="13">
-        <f>38000/160000</f>
-        <v>0.23749999999999999</v>
-      </c>
-      <c r="C85" s="12"/>
-      <c r="D85" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E85" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F85" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G85" s="12"/>
-      <c r="H85" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I85" s="12"/>
-      <c r="J85" s="12"/>
-      <c r="K85" s="12"/>
-      <c r="L85" s="12"/>
-      <c r="M85" s="12"/>
-      <c r="N85" s="12"/>
-      <c r="O85" s="12"/>
-    </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A86" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B86" s="13">
-        <f>0.008/160000</f>
-        <v>4.9999999999999998E-8</v>
-      </c>
-      <c r="C86" s="12"/>
-      <c r="D86" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E86" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F86" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G86" s="12"/>
-      <c r="H86" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I86" s="12"/>
-      <c r="J86" s="12"/>
-      <c r="K86" s="12"/>
-      <c r="L86" s="12"/>
-      <c r="M86" s="12"/>
-      <c r="N86" s="12"/>
-      <c r="O86" s="12"/>
+      <c r="B86" s="8"/>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A87" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B87" s="13">
-        <f>B84*0.0015</f>
-        <v>1.14375E-4</v>
-      </c>
-      <c r="C87" s="12"/>
-      <c r="D87" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E87" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F87" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G87" s="12"/>
-      <c r="H87" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I87" s="12"/>
-      <c r="J87" s="12"/>
-      <c r="K87" s="12"/>
-      <c r="L87" s="12"/>
-      <c r="M87" s="12"/>
-      <c r="N87" s="12"/>
-      <c r="O87" s="12"/>
+      <c r="A87" s="1"/>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A88" s="1"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I89" s="18"/>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B90" s="8"/>
+      <c r="A90" s="3"/>
+      <c r="B90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A91" s="1"/>
+      <c r="A91" s="3"/>
+      <c r="B91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A92" s="1"/>
-      <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1"/>
+      <c r="A92" s="3"/>
+      <c r="B92" s="6"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="I93" s="18"/>
+      <c r="A93" s="3"/>
+      <c r="B93" s="6"/>
+      <c r="D93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A94" s="3"/>
-      <c r="B94" s="3"/>
-      <c r="F94" s="3"/>
-      <c r="G94" s="3"/>
-      <c r="H94" s="3"/>
+      <c r="B94" s="6"/>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A95" s="3"/>
-      <c r="B95" s="3"/>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3"/>
+      <c r="B95" s="6"/>
       <c r="H95" s="3"/>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A96" s="3"/>
       <c r="B96" s="6"/>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3"/>
       <c r="H96" s="3"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="3"/>
       <c r="B97" s="6"/>
-      <c r="D97" s="3"/>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B98" s="6"/>
+      <c r="H98" s="4"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B99" s="6"/>
+      <c r="A99" s="3"/>
+      <c r="B99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
       <c r="H99" s="3"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B100" s="6"/>
+      <c r="B100" s="3"/>
       <c r="H100" s="3"/>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B101" s="6"/>
+      <c r="A101" s="3"/>
+      <c r="B101" s="3"/>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B102" s="6"/>
-      <c r="H102" s="4"/>
+      <c r="B102" s="3"/>
+      <c r="H102" s="3"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="3"/>
+      <c r="A103" s="5"/>
       <c r="B103" s="3"/>
-      <c r="F103" s="3"/>
-      <c r="G103" s="3"/>
+      <c r="C103"/>
+      <c r="D103" s="3"/>
+      <c r="G103"/>
       <c r="H103" s="3"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="5"/>
       <c r="B104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="F104" s="3"/>
+      <c r="G104"/>
       <c r="H104" s="3"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="3"/>
-      <c r="B105" s="3"/>
+      <c r="B105" s="6"/>
+      <c r="C105" s="9"/>
+      <c r="F105" s="3"/>
       <c r="G105" s="3"/>
-      <c r="H105" s="3"/>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B106" s="3"/>
-      <c r="H106" s="3"/>
+      <c r="I105" s="18"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="5"/>
-      <c r="B107" s="3"/>
-      <c r="C107"/>
-      <c r="D107" s="3"/>
-      <c r="G107"/>
-      <c r="H107" s="3"/>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" s="5"/>
-      <c r="B108" s="3"/>
-      <c r="D108" s="3"/>
-      <c r="F108" s="3"/>
-      <c r="G108"/>
-      <c r="H108" s="3"/>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="3"/>
-      <c r="B109" s="6"/>
-      <c r="C109" s="9"/>
-      <c r="F109" s="3"/>
-      <c r="G109" s="3"/>
-      <c r="I109" s="18"/>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="1"/>
-      <c r="B111" s="1"/>
+      <c r="A107" s="1"/>
+      <c r="B107" s="1"/>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" s="1"/>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" s="1"/>
+      <c r="B116" s="1"/>
+      <c r="C116" s="1"/>
+      <c r="D116" s="1"/>
+      <c r="E116" s="1"/>
+      <c r="F116" s="1"/>
+      <c r="G116" s="1"/>
+      <c r="H116" s="1"/>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I117" s="18"/>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" s="3"/>
+      <c r="B118" s="3"/>
+      <c r="G118" s="3"/>
+      <c r="H118" s="3"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" s="1"/>
+      <c r="A119" s="3"/>
+      <c r="B119" s="3"/>
+      <c r="G119" s="3"/>
+      <c r="H119" s="3"/>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120" s="1"/>
-      <c r="B120" s="1"/>
-      <c r="C120" s="1"/>
-      <c r="D120" s="1"/>
-      <c r="E120" s="1"/>
-      <c r="F120" s="1"/>
-      <c r="G120" s="1"/>
-      <c r="H120" s="1"/>
+      <c r="A120" s="3"/>
+      <c r="B120" s="6"/>
+      <c r="G120" s="3"/>
+      <c r="H120" s="3"/>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="I121" s="18"/>
+      <c r="A121" s="5"/>
+      <c r="B121" s="3"/>
+      <c r="C121"/>
+      <c r="D121" s="3"/>
+      <c r="G121"/>
+      <c r="H121" s="3"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="3"/>
+      <c r="A122" s="5"/>
       <c r="B122" s="3"/>
-      <c r="G122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="F122" s="3"/>
+      <c r="G122"/>
       <c r="H122" s="3"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="3"/>
-      <c r="B123" s="3"/>
-      <c r="G123" s="3"/>
-      <c r="H123" s="3"/>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" s="3"/>
-      <c r="B124" s="6"/>
-      <c r="G124" s="3"/>
-      <c r="H124" s="3"/>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A125" s="5"/>
-      <c r="B125" s="3"/>
-      <c r="C125"/>
-      <c r="D125" s="3"/>
-      <c r="G125"/>
-      <c r="H125" s="3"/>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A126" s="5"/>
-      <c r="B126" s="3"/>
-      <c r="D126" s="3"/>
-      <c r="F126" s="3"/>
-      <c r="G126"/>
-      <c r="H126" s="3"/>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A146" s="3"/>
-      <c r="B146" s="3"/>
-      <c r="D146" s="3"/>
-      <c r="G146" s="3"/>
-      <c r="H146" s="3"/>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A147" s="3"/>
-      <c r="B147" s="3"/>
-      <c r="D147" s="3"/>
-      <c r="G147" s="3"/>
-      <c r="H147" s="3"/>
-    </row>
-    <row r="278" spans="13:13" x14ac:dyDescent="0.25">
-      <c r="M278" s="1" t="s">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" s="3"/>
+      <c r="B142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="G142" s="3"/>
+      <c r="H142" s="3"/>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" s="3"/>
+      <c r="B143" s="3"/>
+      <c r="D143" s="3"/>
+      <c r="G143" s="3"/>
+      <c r="H143" s="3"/>
+    </row>
+    <row r="274" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M274" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="13:13" x14ac:dyDescent="0.25">
-      <c r="M287" s="1" t="s">
+    <row r="283" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M283" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M284" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M285" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2883,28 +2780,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="13:13" x14ac:dyDescent="0.25">
-      <c r="M292" s="1" t="s">
+    <row r="290" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M290" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="13:13" x14ac:dyDescent="0.25">
-      <c r="M293" s="1" t="s">
+    <row r="291" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M291" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="13:13" x14ac:dyDescent="0.25">
-      <c r="M294" s="1" t="s">
+    <row r="301" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M301" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="13:13" x14ac:dyDescent="0.25">
-      <c r="M295" s="1" t="s">
+    <row r="302" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M302" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="13:13" x14ac:dyDescent="0.25">
-      <c r="M305" s="1" t="s">
+    <row r="303" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M303" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2918,23 +2815,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="13:13" x14ac:dyDescent="0.25">
-      <c r="M310" s="1" t="s">
+    <row r="308" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M308" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="13:13" x14ac:dyDescent="0.25">
-      <c r="M311" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="312" spans="13:13" x14ac:dyDescent="0.25">
-      <c r="M312" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="313" spans="13:13" x14ac:dyDescent="0.25">
-      <c r="M313" s="1" t="s">
+    <row r="309" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M309" s="1" t="s">
         <v>1</v>
       </c>
     </row>
